--- a/docs/um-de-verificat.xlsx
+++ b/docs/um-de-verificat.xlsx
@@ -52,10 +52,10 @@
     <t>BUC</t>
   </si>
   <si>
-    <t>VERIFICĂ MAPAREA</t>
-  </si>
-  <si>
-    <t>unitățile nu se convertesc — probabil e alt articol</t>
+    <t>PREȚ NEFOLOSIBIL</t>
+  </si>
+  <si>
+    <t>unități diferite: prețul din nomenclator nu se poate înmulți cu cantitatea</t>
   </si>
   <si>
     <t>0.05 – 0.7</t>
